--- a/artfynd/S 921-2026 artfynd.xlsx
+++ b/artfynd/S 921-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100441950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100442091</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108851269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101540089</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100453557</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100453558</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100453560</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108765727</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108766578</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74767752</t>
         </is>
       </c>
     </row>
@@ -1871,6 +1926,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102195083</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1982,6 +2042,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75158032</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74470771</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2199,6 +2269,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100441952</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2310,6 +2385,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74083289</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2421,6 +2501,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75061449</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101071435</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2665,6 +2755,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102205479</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2787,6 +2882,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100759518</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2909,6 +3009,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100759646</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3020,6 +3125,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74770452</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3131,6 +3241,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982761</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3242,6 +3357,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74412026</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3353,6 +3473,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74844334</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3464,6 +3589,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74561110</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3575,6 +3705,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75143991</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3686,6 +3821,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74783471</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3793,8 +3933,43 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74464022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>